--- a/java/spring/spring-context.xlsx
+++ b/java/spring/spring-context.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21648" windowHeight="9155"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="2" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.context" sheetId="1" r:id="rId1"/>
@@ -17,13 +17,14 @@
     <sheet name="index.processor" sheetId="8" r:id="rId8"/>
     <sheet name="support" sheetId="9" r:id="rId9"/>
     <sheet name="weaving" sheetId="10" r:id="rId10"/>
+    <sheet name="org.springframework.validation." sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="262">
   <si>
     <t>ApplicationContext</t>
   </si>
@@ -3362,6 +3363,83 @@
   </si>
   <si>
     <t>LoadTimeWeaverAwareProcessor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BeanValidationPostProcessor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CustomValidatorBean</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LocaleContextMessageInterpolator</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LocalValidatorFactoryBean</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MessageSourceResourceBundleLocator</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MethodValidationInterceptor</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MethodValidationPostProcessor</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3374,13 +3452,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -3901,10 +3985,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3913,34 +3997,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3952,98 +4033,101 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4051,16 +4135,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4068,7 +4152,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4403,7 +4490,7 @@
       </c>
     </row>
     <row r="2" spans="2:2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4423,7 +4510,7 @@
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4433,7 +4520,7 @@
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4443,7 +4530,7 @@
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4453,7 +4540,7 @@
       </c>
     </row>
     <row r="12" spans="2:2">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4463,17 +4550,17 @@
       </c>
     </row>
     <row r="14" spans="2:2">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="25.2" spans="1:1">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:2">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4493,7 +4580,7 @@
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -4503,7 +4590,7 @@
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4523,7 +4610,7 @@
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4533,7 +4620,7 @@
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4543,7 +4630,7 @@
       </c>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -4553,7 +4640,7 @@
       </c>
     </row>
     <row r="32" spans="2:2">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4583,7 +4670,7 @@
       </c>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4603,7 +4690,7 @@
       </c>
     </row>
     <row r="42" spans="2:2">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4678,6 +4765,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:A9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="62.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" ht="15.6" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" ht="15.6" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" ht="15.6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" ht="15.6" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" ht="15.6" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -4689,767 +4826,767 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="25.2" spans="1:2">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" ht="28.8" spans="1:2">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="4"/>
+      <c r="B7" s="5"/>
     </row>
     <row r="8" ht="28.8" spans="1:2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" ht="28.8" spans="1:2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="4"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="4"/>
+      <c r="B13" s="5"/>
     </row>
     <row r="14" ht="42.6" spans="1:2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="4"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" ht="42" spans="1:2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="4"/>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" ht="28.8" spans="1:2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="4"/>
+      <c r="B19" s="5"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4" t="s">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" s="5"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="24" ht="28.2" spans="1:2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" s="5"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5" t="s">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="4"/>
+      <c r="B27" s="5"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="4"/>
+      <c r="B29" s="5"/>
     </row>
     <row r="30" ht="27.6" spans="1:2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="5"/>
+      <c r="B30" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="4"/>
+      <c r="B31" s="5"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" s="5"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5" t="s">
+      <c r="A34" s="5"/>
+      <c r="B34" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B35" s="4"/>
+      <c r="B35" s="5"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5" t="s">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="4"/>
+      <c r="B37" s="5"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4" t="s">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="4"/>
+      <c r="B39" s="5"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4" t="s">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" s="5"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4" t="s">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B43" s="4"/>
+      <c r="B43" s="5"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4" t="s">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="4"/>
+      <c r="B45" s="5"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4" t="s">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="4"/>
+      <c r="B47" s="5"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="7" t="s">
+      <c r="A48" s="5"/>
+      <c r="B48" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="4"/>
+      <c r="B49" s="5"/>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4" t="s">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="4"/>
+      <c r="B51" s="5"/>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4" t="s">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B53" s="4"/>
+      <c r="B53" s="5"/>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B55" s="4"/>
+      <c r="B55" s="5"/>
     </row>
     <row r="56" ht="43.2" spans="1:2">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5" t="s">
+      <c r="A56" s="5"/>
+      <c r="B56" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B57" s="4"/>
+      <c r="B57" s="5"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4" t="s">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B59" s="4"/>
+      <c r="B59" s="5"/>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5" t="s">
+      <c r="A60" s="5"/>
+      <c r="B60" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B61" s="4"/>
+      <c r="B61" s="5"/>
     </row>
     <row r="62" ht="28.2" spans="1:2">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="5"/>
+      <c r="B62" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B63" s="4"/>
+      <c r="B63" s="5"/>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5" t="s">
+      <c r="A64" s="5"/>
+      <c r="B64" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B65" s="4"/>
+      <c r="B65" s="5"/>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5" t="s">
+      <c r="A66" s="5"/>
+      <c r="B66" s="6" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B67" s="4"/>
+      <c r="B67" s="5"/>
     </row>
     <row r="68" ht="28.8" spans="1:2">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5" t="s">
+      <c r="A68" s="5"/>
+      <c r="B68" s="6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B69" s="4"/>
+      <c r="B69" s="5"/>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4" t="s">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B71" s="4"/>
+      <c r="B71" s="5"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5" t="s">
+      <c r="A72" s="5"/>
+      <c r="B72" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B73" s="4"/>
+      <c r="B73" s="5"/>
     </row>
     <row r="74" ht="28.8" spans="1:2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5" t="s">
+      <c r="A74" s="5"/>
+      <c r="B74" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="4"/>
+      <c r="B75" s="5"/>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4" t="s">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="4"/>
+      <c r="B77" s="5"/>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4" t="s">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B79" s="4"/>
+      <c r="B79" s="5"/>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4" t="s">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B81" s="4"/>
+      <c r="B81" s="5"/>
     </row>
     <row r="82" ht="28.8" spans="1:2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="5" t="s">
+      <c r="A82" s="5"/>
+      <c r="B82" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B83" s="4"/>
+      <c r="B83" s="5"/>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="5" t="s">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B85" s="4"/>
+      <c r="B85" s="5"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4" t="s">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B87" s="4"/>
+      <c r="B87" s="5"/>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="5" t="s">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="4"/>
+      <c r="B89" s="5"/>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4" t="s">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B91" s="4"/>
+      <c r="B91" s="5"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4" t="s">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B93" s="4"/>
+      <c r="B93" s="5"/>
     </row>
     <row r="94" ht="28.8" spans="1:2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="5" t="s">
+      <c r="A94" s="5"/>
+      <c r="B94" s="6" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B95" s="4"/>
+      <c r="B95" s="5"/>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="4"/>
-      <c r="B96" s="5" t="s">
+      <c r="A96" s="5"/>
+      <c r="B96" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B97" s="4"/>
+      <c r="B97" s="5"/>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4" t="s">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B99" s="4"/>
+      <c r="B99" s="5"/>
     </row>
     <row r="100" ht="28.8" spans="1:2">
-      <c r="A100" s="4"/>
-      <c r="B100" s="5" t="s">
+      <c r="A100" s="5"/>
+      <c r="B100" s="6" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B101" s="4"/>
+      <c r="B101" s="5"/>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4" t="s">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B103" s="4"/>
+      <c r="B103" s="5"/>
     </row>
     <row r="104" ht="27.6" spans="1:2">
-      <c r="A104" s="4"/>
-      <c r="B104" s="5" t="s">
+      <c r="A104" s="5"/>
+      <c r="B104" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B105" s="4"/>
+      <c r="B105" s="5"/>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4" t="s">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B107" s="4"/>
+      <c r="B107" s="5"/>
     </row>
     <row r="108" ht="28.8" spans="1:2">
-      <c r="A108" s="4"/>
-      <c r="B108" s="5" t="s">
+      <c r="A108" s="5"/>
+      <c r="B108" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B109" s="4"/>
+      <c r="B109" s="5"/>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4" t="s">
+      <c r="A110" s="5"/>
+      <c r="B110" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B111" s="4"/>
+      <c r="B111" s="5"/>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="4"/>
-      <c r="B112" s="5" t="s">
+      <c r="A112" s="5"/>
+      <c r="B112" s="6" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B113" s="4"/>
+      <c r="B113" s="5"/>
     </row>
     <row r="114" ht="28.8" spans="1:2">
-      <c r="A114" s="4"/>
-      <c r="B114" s="5" t="s">
+      <c r="A114" s="5"/>
+      <c r="B114" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B115" s="4"/>
+      <c r="B115" s="5"/>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4" t="s">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B117" s="4"/>
+      <c r="B117" s="5"/>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="4"/>
-      <c r="B118" s="5" t="s">
+      <c r="A118" s="5"/>
+      <c r="B118" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B119" s="4"/>
-      <c r="D119" s="4"/>
+      <c r="B119" s="5"/>
+      <c r="D119" s="5"/>
     </row>
     <row r="120" ht="27.6" spans="1:2">
-      <c r="A120" s="4"/>
-      <c r="B120" s="5" t="s">
+      <c r="A120" s="5"/>
+      <c r="B120" s="6" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B121" s="4"/>
+      <c r="B121" s="5"/>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="4"/>
-      <c r="B122" s="5" t="s">
+      <c r="A122" s="5"/>
+      <c r="B122" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B123" s="4"/>
+      <c r="B123" s="5"/>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="4"/>
-      <c r="B124" s="5" t="s">
+      <c r="A124" s="5"/>
+      <c r="B124" s="6" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="126" ht="27.6" spans="2:2">
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="128" ht="43.2" spans="2:2">
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="9" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5481,7 +5618,7 @@
       </c>
     </row>
     <row r="2" ht="34" customHeight="1" spans="2:2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5491,7 +5628,7 @@
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5506,12 +5643,12 @@
       </c>
     </row>
     <row r="7" ht="25.2" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="8" ht="56.4" spans="2:2">
-      <c r="B8" s="2" t="s">
+    <row r="8" ht="42.6" spans="2:2">
+      <c r="B8" s="3" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5520,8 +5657,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" ht="56.4" spans="2:2">
-      <c r="B10" s="2" t="s">
+    <row r="10" ht="42" spans="2:2">
+      <c r="B10" s="3" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5530,8 +5667,8 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" ht="27.6" spans="2:2">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:2">
+      <c r="B12" s="3" t="s">
         <v>185</v>
       </c>
     </row>
@@ -5550,8 +5687,8 @@
     <col min="1" max="1" width="25.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5576,7 +5713,7 @@
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5807,8 +5944,8 @@
     <col min="1" max="1" width="38.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.2" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5818,7 +5955,7 @@
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>191</v>
       </c>
     </row>

--- a/java/spring/spring-context.xlsx
+++ b/java/spring/spring-context.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="2" activeTab="10"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.context" sheetId="1" r:id="rId1"/>

--- a/java/spring/spring-context.xlsx
+++ b/java/spring/spring-context.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="org.springframework.context" sheetId="1" r:id="rId1"/>
